--- a/import_siswa_sikapdik/Template_Import_Siswa_SIKAPDIK_Kelas6.xlsx
+++ b/import_siswa_sikapdik/Template_Import_Siswa_SIKAPDIK_Kelas6.xlsx
@@ -642,9 +642,21 @@
           <t>Aditya Rifqi Nurfiansah</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>12/04/2014</t>
+        </is>
+      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 01/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -670,9 +682,21 @@
           <t>Aisya Awanda Santika</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>08/03/2014</t>
+        </is>
+      </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Dusun Sempu, RT 02/RW 05, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -698,9 +722,21 @@
           <t>Chantika Hummayra Annanta</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>21/06/2014</t>
+        </is>
+      </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>Dusun Sempu, RT 02/RW 07, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -726,9 +762,21 @@
           <t>Doni Ardianto</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>17/01/2014</t>
+        </is>
+      </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 01/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -754,9 +802,21 @@
           <t>Faiz Fatkhur Rohman</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>22/03/2014</t>
+        </is>
+      </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 03/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -782,9 +842,21 @@
           <t>Nafisha Mikayla Agatha</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>28/05/2014</t>
+        </is>
+      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>Dusun Sempu, RT 02/RW 07, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -810,9 +882,21 @@
           <t>Naura Novelia Putri</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2013</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 02/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -838,9 +922,21 @@
           <t>Raia Vemdya Kasih</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>18/11/2013</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 01/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -866,9 +962,21 @@
           <t>Raisya Septiana</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>19/09/2014</t>
+        </is>
+      </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>Dusun Sempu, RT 02/RW 07, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -894,9 +1002,21 @@
           <t>Silva Alexa Revandra</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Pacitan</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>03/09/2013</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 03/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -922,9 +1042,21 @@
           <t>Yasmina Lika Rusyani</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Bengkalis</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>28/05/2014</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 2, RT 02/RW 09, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
@@ -950,9 +1082,21 @@
           <t>Zaky Ahsan Baihaqi</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Bekasi</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>23/06/2013</t>
+        </is>
+      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>Dusun Plapar 1, RT 03/RW 08, Desa Jatigunung, Kec. Tulakan, Kab. Pacitan</t>
